--- a/Budgeting System_Manpower Template.xlsx
+++ b/Budgeting System_Manpower Template.xlsx
@@ -8,17 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oclpholdings-my.sharepoint.com/personal/jumalonpvp_ortigas_com_ph/Documents/Documents/Budgeting System/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="469" documentId="8_{B440BBE7-9F96-47D5-8577-254065B29B2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B13AF29F-5105-4215-A023-98C995CB7562}"/>
+  <xr:revisionPtr revIDLastSave="795" documentId="8_{B440BBE7-9F96-47D5-8577-254065B29B2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F69A86D3-42DF-48D7-B5FE-9375C3382155}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{09E9E6D6-0F48-4124-9B86-4777CBE4DCA7}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="3" xr2:uid="{09E9E6D6-0F48-4124-9B86-4777CBE4DCA7}"/>
   </bookViews>
   <sheets>
     <sheet name="Employee List" sheetId="5" r:id="rId1"/>
-    <sheet name="Average Salary" sheetId="6" r:id="rId2"/>
-    <sheet name="SSS" sheetId="9" state="hidden" r:id="rId3"/>
+    <sheet name="Computed Monthly Salary" sheetId="11" r:id="rId2"/>
+    <sheet name="Average Salary" sheetId="6" r:id="rId3"/>
+    <sheet name="Headcount per Company" sheetId="10" r:id="rId4"/>
+    <sheet name="SSS" sheetId="9" state="hidden" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Employee List'!$A$7:$F$356</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Employee List'!$A$7:$F$351</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -70,8 +72,35 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={A9227E08-A629-4384-89D7-E972BF5BBF33}</author>
+    <author>tc={7586A55B-0E67-4A7B-AB78-292ABD9BA314}</author>
+  </authors>
+  <commentList>
+    <comment ref="A6" authorId="0" shapeId="0" xr:uid="{A9227E08-A629-4384-89D7-E972BF5BBF33}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Project-based</t>
+      </text>
+    </comment>
+    <comment ref="A7" authorId="1" shapeId="0" xr:uid="{7586A55B-0E67-4A7B-AB78-292ABD9BA314}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Outsourced</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="38">
   <si>
     <t>Government Contributions (ER) - SSS</t>
   </si>
@@ -88,13 +117,7 @@
     <t>Company</t>
   </si>
   <si>
-    <t>Level</t>
-  </si>
-  <si>
     <t>Average Salary</t>
-  </si>
-  <si>
-    <t>Average Salary per Employee Level</t>
   </si>
   <si>
     <t>Employee List</t>
@@ -157,22 +180,40 @@
     <t>4. Table values reflect SSS Circular No. 2024-006 guidelines effective January 2025.</t>
   </si>
   <si>
-    <t>Ortigas &amp; Company, Limited Partnership</t>
-  </si>
-  <si>
-    <t>Ortigas Commercial Corporation</t>
-  </si>
-  <si>
-    <t>Ortigas Land Corporation</t>
-  </si>
-  <si>
-    <t>OUTSOURCED</t>
-  </si>
-  <si>
     <t>to be filled-out by HR</t>
   </si>
   <si>
     <t>Ortigas Group (OLC, OCC, OCLP)</t>
+  </si>
+  <si>
+    <t>Average Salary per Employee Rank</t>
+  </si>
+  <si>
+    <t>OLC</t>
+  </si>
+  <si>
+    <t>OCC</t>
+  </si>
+  <si>
+    <t>OCLP</t>
+  </si>
+  <si>
+    <t>Rank</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Current Headcount per Company</t>
+  </si>
+  <si>
+    <t>Account</t>
+  </si>
+  <si>
+    <t>Salary</t>
+  </si>
+  <si>
+    <t>Guaranteed Bonus</t>
   </si>
 </sst>
 </file>
@@ -183,7 +224,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -254,6 +295,15 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -293,7 +343,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -331,13 +381,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -371,6 +430,17 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -734,9 +804,20 @@
 </ThreadedComments>
 </file>
 
+<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="A6" dT="2026-07-30T06:31:58.77" personId="{1665D72D-25BF-423C-963A-1B92BF1BAA5B}" id="{A9227E08-A629-4384-89D7-E972BF5BBF33}">
+    <text>Project-based</text>
+  </threadedComment>
+  <threadedComment ref="A7" dT="2026-07-30T06:32:05.15" personId="{1665D72D-25BF-423C-963A-1B92BF1BAA5B}" id="{7586A55B-0E67-4A7B-AB78-292ABD9BA314}">
+    <text>Outsourced</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{789E7D11-EEEA-4C1D-B28D-993BA3CC8ADE}">
-  <dimension ref="A1:H356"/>
+  <dimension ref="A1:H351"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="34" bestFit="1" customWidth="1"/>
@@ -745,18 +826,18 @@
     <col min="4" max="4" width="35.453125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="39.08984375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="40.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.81640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -764,27 +845,27 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C4" s="15">
         <f>SUBTOTAL(9,C8:C1048576)</f>
-        <v>27318101.290754721</v>
+        <v>26655176.712973587</v>
       </c>
       <c r="D4" s="15">
         <f>SUBTOTAL(9,D8:D1048576)</f>
-        <v>1101000</v>
+        <v>1083850</v>
       </c>
       <c r="E4" s="15">
         <f>SUBTOTAL(9,E8:E1048576)</f>
-        <v>66000</v>
+        <v>65000</v>
       </c>
       <c r="F4" s="15">
         <f>SUBTOTAL(9,F8:F1048576)</f>
-        <v>458011.23413999996</v>
+        <v>448362.70459999994</v>
       </c>
       <c r="G4" s="16">
-        <f>SUM(D4:F4)</f>
-        <v>1625011.2341399998</v>
+        <f>SUM(C4:F4)</f>
+        <v>28252389.417573586</v>
       </c>
       <c r="H4" s="1"/>
     </row>
@@ -793,22 +874,22 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -816,7 +897,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="C7" s="17" t="s">
         <v>3</v>
@@ -833,7 +914,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B8" s="4">
         <v>3</v>
@@ -857,7 +938,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B9" s="4">
         <v>1</v>
@@ -881,7 +962,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B10" s="4">
         <v>1</v>
@@ -905,7 +986,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B11" s="4">
         <v>1</v>
@@ -929,7 +1010,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B12" s="4">
         <v>4</v>
@@ -953,7 +1034,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B13" s="4">
         <v>3</v>
@@ -977,7 +1058,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B14" s="4">
         <v>7</v>
@@ -1001,7 +1082,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B15" s="4">
         <v>1</v>
@@ -1025,7 +1106,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B16" s="4">
         <v>1</v>
@@ -1049,7 +1130,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B17" s="4">
         <v>7</v>
@@ -1073,7 +1154,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B18" s="4">
         <v>4</v>
@@ -1097,7 +1178,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B19" s="4">
         <v>4</v>
@@ -1121,7 +1202,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B20" s="4">
         <v>4</v>
@@ -1145,7 +1226,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B21" s="4">
         <v>1</v>
@@ -1169,7 +1250,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B22" s="4">
         <v>8</v>
@@ -1193,7 +1274,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B23" s="4">
         <v>3</v>
@@ -1217,7 +1298,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B24" s="4">
         <v>3</v>
@@ -1241,7 +1322,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B25" s="4">
         <v>3</v>
@@ -1265,7 +1346,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B26" s="4">
         <v>6</v>
@@ -1289,7 +1370,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B27" s="4">
         <v>5</v>
@@ -1313,7 +1394,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B28" s="4">
         <v>1</v>
@@ -1337,7 +1418,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B29" s="4">
         <v>8</v>
@@ -1361,7 +1442,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B30" s="4">
         <v>4</v>
@@ -1385,7 +1466,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B31" s="4">
         <v>7</v>
@@ -1409,7 +1490,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B32" s="4">
         <v>1</v>
@@ -1433,7 +1514,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B33" s="4">
         <v>1</v>
@@ -1457,7 +1538,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B34" s="4">
         <v>3</v>
@@ -1481,7 +1562,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B35" s="4">
         <v>5</v>
@@ -1505,7 +1586,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B36" s="4">
         <v>1</v>
@@ -1529,7 +1610,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B37" s="4">
         <v>5</v>
@@ -1553,7 +1634,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B38" s="4">
         <v>3</v>
@@ -1577,7 +1658,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B39" s="4">
         <v>1</v>
@@ -1601,7 +1682,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B40" s="4">
         <v>1</v>
@@ -1625,7 +1706,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B41" s="4">
         <v>4</v>
@@ -1649,7 +1730,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B42" s="4">
         <v>5</v>
@@ -1673,7 +1754,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B43" s="4">
         <v>3</v>
@@ -1697,7 +1778,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B44" s="4">
         <v>5</v>
@@ -1721,7 +1802,7 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B45" s="4">
         <v>3</v>
@@ -1745,7 +1826,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B46" s="4">
         <v>1</v>
@@ -1769,7 +1850,7 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B47" s="4">
         <v>8</v>
@@ -1793,7 +1874,7 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B48" s="4">
         <v>5</v>
@@ -1817,7 +1898,7 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B49" s="4">
         <v>4</v>
@@ -1841,7 +1922,7 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B50" s="4">
         <v>5</v>
@@ -1865,7 +1946,7 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B51" s="4">
         <v>5</v>
@@ -1889,7 +1970,7 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B52" s="4">
         <v>3</v>
@@ -1913,7 +1994,7 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B53" s="4">
         <v>5</v>
@@ -1937,7 +2018,7 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B54" s="4">
         <v>4</v>
@@ -1961,7 +2042,7 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B55" s="4">
         <v>1</v>
@@ -1985,7 +2066,7 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B56" s="4">
         <v>8</v>
@@ -2009,7 +2090,7 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B57" s="4">
         <v>5</v>
@@ -2033,7 +2114,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B58" s="4">
         <v>1</v>
@@ -2057,7 +2138,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B59" s="4">
         <v>8</v>
@@ -2081,7 +2162,7 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B60" s="4">
         <v>5</v>
@@ -2105,7 +2186,7 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B61" s="4">
         <v>3</v>
@@ -2129,7 +2210,7 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B62" s="4">
         <v>4</v>
@@ -2153,7 +2234,7 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B63" s="4">
         <v>3</v>
@@ -2177,7 +2258,7 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B64" s="4">
         <v>1</v>
@@ -2201,7 +2282,7 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B65" s="4">
         <v>3</v>
@@ -2225,7 +2306,7 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B66" s="4">
         <v>8</v>
@@ -2249,7 +2330,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B67" s="4">
         <v>3</v>
@@ -2273,7 +2354,7 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B68" s="4">
         <v>5</v>
@@ -2297,7 +2378,7 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B69" s="4">
         <v>5</v>
@@ -2321,7 +2402,7 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B70" s="4">
         <v>3</v>
@@ -2345,7 +2426,7 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B71" s="4">
         <v>3</v>
@@ -2369,7 +2450,7 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B72" s="4">
         <v>6</v>
@@ -2393,7 +2474,7 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B73" s="4">
         <v>3</v>
@@ -2417,7 +2498,7 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B74" s="4">
         <v>4</v>
@@ -2441,7 +2522,7 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B75" s="4">
         <v>3</v>
@@ -2465,7 +2546,7 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B76" s="4">
         <v>7</v>
@@ -2489,7 +2570,7 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B77" s="4">
         <v>5</v>
@@ -2513,7 +2594,7 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B78" s="4">
         <v>4</v>
@@ -2537,7 +2618,7 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B79" s="4">
         <v>7</v>
@@ -2561,7 +2642,7 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B80" s="4">
         <v>4</v>
@@ -2585,7 +2666,7 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B81" s="4">
         <v>3</v>
@@ -2609,7 +2690,7 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B82" s="4">
         <v>8</v>
@@ -2633,7 +2714,7 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B83" s="4">
         <v>3</v>
@@ -2657,7 +2738,7 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B84" s="4">
         <v>3</v>
@@ -2681,7 +2762,7 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B85" s="4">
         <v>4</v>
@@ -2705,7 +2786,7 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B86" s="4">
         <v>6</v>
@@ -2729,7 +2810,7 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B87" s="4">
         <v>4</v>
@@ -2753,7 +2834,7 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B88" s="4">
         <v>7</v>
@@ -2777,7 +2858,7 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B89" s="4">
         <v>3</v>
@@ -2801,7 +2882,7 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B90" s="4">
         <v>4</v>
@@ -2825,7 +2906,7 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B91" s="4">
         <v>4</v>
@@ -2849,7 +2930,7 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B92" s="4">
         <v>4</v>
@@ -2873,7 +2954,7 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B93" s="4">
         <v>3</v>
@@ -2897,7 +2978,7 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B94" s="4">
         <v>3</v>
@@ -2921,7 +3002,7 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B95" s="4">
         <v>5</v>
@@ -2945,7 +3026,7 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B96" s="4">
         <v>5</v>
@@ -2969,7 +3050,7 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B97" s="4">
         <v>5</v>
@@ -2993,7 +3074,7 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B98" s="4">
         <v>4</v>
@@ -3017,7 +3098,7 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A99" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B99" s="4">
         <v>5</v>
@@ -3041,7 +3122,7 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B100" s="4">
         <v>9</v>
@@ -3065,7 +3146,7 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B101" s="4">
         <v>3</v>
@@ -3089,7 +3170,7 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A102" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B102" s="4">
         <v>8</v>
@@ -3113,7 +3194,7 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A103" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B103" s="4">
         <v>5</v>
@@ -3137,7 +3218,7 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A104" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B104" s="4">
         <v>5</v>
@@ -3161,7 +3242,7 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A105" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B105" s="4">
         <v>4</v>
@@ -3185,7 +3266,7 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A106" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B106" s="4">
         <v>4</v>
@@ -3209,7 +3290,7 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A107" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B107" s="4">
         <v>6</v>
@@ -3233,7 +3314,7 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B108" s="4">
         <v>3</v>
@@ -3257,7 +3338,7 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B109" s="4">
         <v>5</v>
@@ -3281,7 +3362,7 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A110" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B110" s="4">
         <v>7</v>
@@ -3305,7 +3386,7 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A111" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B111" s="4">
         <v>3</v>
@@ -3329,7 +3410,7 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B112" s="4">
         <v>5</v>
@@ -3353,7 +3434,7 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A113" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B113" s="4">
         <v>5</v>
@@ -3377,7 +3458,7 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A114" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B114" s="4">
         <v>3</v>
@@ -3401,7 +3482,7 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A115" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B115" s="4">
         <v>7</v>
@@ -3425,7 +3506,7 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A116" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B116" s="4">
         <v>6</v>
@@ -3449,7 +3530,7 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A117" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B117" s="4">
         <v>3</v>
@@ -3473,7 +3554,7 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A118" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B118" s="4">
         <v>5</v>
@@ -3497,7 +3578,7 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A119" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B119" s="4">
         <v>5</v>
@@ -3521,7 +3602,7 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A120" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B120" s="4">
         <v>3</v>
@@ -3545,7 +3626,7 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A121" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B121" s="4">
         <v>7</v>
@@ -3569,7 +3650,7 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A122" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B122" s="4">
         <v>3</v>
@@ -3593,7 +3674,7 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A123" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B123" s="4">
         <v>4</v>
@@ -3617,7 +3698,7 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A124" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B124" s="4">
         <v>5</v>
@@ -3641,7 +3722,7 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A125" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B125" s="4">
         <v>3</v>
@@ -3665,7 +3746,7 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A126" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B126" s="4">
         <v>3</v>
@@ -3689,7 +3770,7 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A127" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B127" s="4">
         <v>6</v>
@@ -3713,7 +3794,7 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A128" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B128" s="4">
         <v>5</v>
@@ -3737,7 +3818,7 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A129" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B129" s="4">
         <v>5</v>
@@ -3761,7 +3842,7 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A130" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B130" s="4">
         <v>5</v>
@@ -3785,7 +3866,7 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A131" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B131" s="4">
         <v>5</v>
@@ -3809,7 +3890,7 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A132" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B132" s="4">
         <v>7</v>
@@ -3833,7 +3914,7 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A133" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B133" s="4">
         <v>4</v>
@@ -3857,7 +3938,7 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A134" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B134" s="4">
         <v>5</v>
@@ -3881,7 +3962,7 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A135" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B135" s="4">
         <v>8</v>
@@ -3905,7 +3986,7 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A136" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B136" s="4">
         <v>4</v>
@@ -3929,7 +4010,7 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A137" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B137" s="4">
         <v>8</v>
@@ -3953,7 +4034,7 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A138" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B138" s="4">
         <v>7</v>
@@ -3977,7 +4058,7 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A139" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B139" s="4">
         <v>6</v>
@@ -4001,7 +4082,7 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A140" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B140" s="4">
         <v>5</v>
@@ -4025,7 +4106,7 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A141" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B141" s="4">
         <v>5</v>
@@ -4049,7 +4130,7 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A142" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B142" s="4">
         <v>5</v>
@@ -4073,7 +4154,7 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A143" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B143" s="4">
         <v>5</v>
@@ -4097,7 +4178,7 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A144" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B144" s="4">
         <v>7</v>
@@ -4121,7 +4202,7 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A145" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B145" s="4">
         <v>4</v>
@@ -4145,7 +4226,7 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A146" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B146" s="4">
         <v>4</v>
@@ -4169,7 +4250,7 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A147" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B147" s="4">
         <v>5</v>
@@ -4193,7 +4274,7 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A148" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B148" s="4">
         <v>5</v>
@@ -4217,7 +4298,7 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A149" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B149" s="4">
         <v>3</v>
@@ -4241,7 +4322,7 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A150" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B150" s="4">
         <v>4</v>
@@ -4265,7 +4346,7 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A151" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B151" s="4">
         <v>4</v>
@@ -4289,7 +4370,7 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A152" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B152" s="4">
         <v>7</v>
@@ -4313,7 +4394,7 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A153" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B153" s="4">
         <v>3</v>
@@ -4337,7 +4418,7 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A154" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B154" s="4">
         <v>8</v>
@@ -4361,7 +4442,7 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A155" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B155" s="4">
         <v>8</v>
@@ -4385,7 +4466,7 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A156" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B156" s="4">
         <v>3</v>
@@ -4409,7 +4490,7 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A157" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B157" s="4">
         <v>3</v>
@@ -4433,7 +4514,7 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A158" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B158" s="4">
         <v>8</v>
@@ -4457,7 +4538,7 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A159" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B159" s="4">
         <v>5</v>
@@ -4481,7 +4562,7 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A160" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B160" s="4">
         <v>8</v>
@@ -4505,7 +4586,7 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A161" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B161" s="4">
         <v>4</v>
@@ -4529,7 +4610,7 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A162" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B162" s="4">
         <v>3</v>
@@ -4553,7 +4634,7 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B163" s="4">
         <v>6</v>
@@ -4577,7 +4658,7 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A164" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B164" s="4">
         <v>6</v>
@@ -4601,7 +4682,7 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A165" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B165" s="4">
         <v>10</v>
@@ -4625,7 +4706,7 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A166" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B166" s="4">
         <v>6</v>
@@ -4649,7 +4730,7 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A167" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B167" s="4">
         <v>6</v>
@@ -4673,7 +4754,7 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A168" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B168" s="4">
         <v>8</v>
@@ -4697,7 +4778,7 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A169" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B169" s="4">
         <v>3</v>
@@ -4721,7 +4802,7 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A170" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B170" s="4">
         <v>5</v>
@@ -4745,7 +4826,7 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A171" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B171" s="4">
         <v>7</v>
@@ -4769,7 +4850,7 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A172" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B172" s="4">
         <v>7</v>
@@ -4793,7 +4874,7 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A173" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B173" s="4">
         <v>7</v>
@@ -4817,7 +4898,7 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A174" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B174" s="4">
         <v>10</v>
@@ -4841,7 +4922,7 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A175" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B175" s="4">
         <v>4</v>
@@ -4865,7 +4946,7 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A176" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B176" s="4">
         <v>5</v>
@@ -4889,7 +4970,7 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A177" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B177" s="4">
         <v>11</v>
@@ -4913,7 +4994,7 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A178" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B178" s="4">
         <v>4</v>
@@ -4937,7 +5018,7 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A179" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B179" s="4">
         <v>9</v>
@@ -4961,7 +5042,7 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A180" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B180" s="4">
         <v>10</v>
@@ -4985,7 +5066,7 @@
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A181" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B181" s="4">
         <v>9</v>
@@ -5009,7 +5090,7 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A182" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B182" s="4">
         <v>4</v>
@@ -5033,18 +5114,18 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A183" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B183" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C183" s="14">
         <f>_xlfn.XLOOKUP(B183,'Average Salary'!A:A,'Average Salary'!B:B)</f>
-        <v>25070.000000000004</v>
+        <v>32379.409200000002</v>
       </c>
       <c r="D183" s="14">
         <f>_xlfn.XLOOKUP($B183,'Average Salary'!$A:$A,'Average Salary'!C:C)</f>
-        <v>2530</v>
+        <v>3280</v>
       </c>
       <c r="E183" s="14">
         <f>_xlfn.XLOOKUP($B183,'Average Salary'!$A:$A,'Average Salary'!D:D)</f>
@@ -5052,12 +5133,12 @@
       </c>
       <c r="F183" s="14">
         <f>_xlfn.XLOOKUP($B183,'Average Salary'!$A:$A,'Average Salary'!E:E)</f>
-        <v>626.75000000000011</v>
+        <v>809.48523000000012</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A184" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B184" s="4">
         <v>1</v>
@@ -5081,7 +5162,7 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A185" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B185" s="4">
         <v>6</v>
@@ -5105,18 +5186,18 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A186" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B186" s="4">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C186" s="14">
         <f>_xlfn.XLOOKUP(B186,'Average Salary'!A:A,'Average Salary'!B:B)</f>
-        <v>78480</v>
+        <v>32379.409200000002</v>
       </c>
       <c r="D186" s="14">
         <f>_xlfn.XLOOKUP($B186,'Average Salary'!$A:$A,'Average Salary'!C:C)</f>
-        <v>3530</v>
+        <v>3280</v>
       </c>
       <c r="E186" s="14">
         <f>_xlfn.XLOOKUP($B186,'Average Salary'!$A:$A,'Average Salary'!D:D)</f>
@@ -5124,12 +5205,12 @@
       </c>
       <c r="F186" s="14">
         <f>_xlfn.XLOOKUP($B186,'Average Salary'!$A:$A,'Average Salary'!E:E)</f>
-        <v>1962</v>
+        <v>809.48523000000012</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A187" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B187" s="4">
         <v>1</v>
@@ -5153,7 +5234,7 @@
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A188" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B188" s="4">
         <v>4</v>
@@ -5177,7 +5258,7 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A189" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B189" s="4">
         <v>6</v>
@@ -5201,7 +5282,7 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A190" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B190" s="4">
         <v>5</v>
@@ -5225,7 +5306,7 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A191" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B191" s="4">
         <v>3</v>
@@ -5249,7 +5330,7 @@
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A192" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B192" s="4">
         <v>11</v>
@@ -5273,7 +5354,7 @@
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A193" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B193" s="4">
         <v>4</v>
@@ -5297,7 +5378,7 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A194" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B194" s="4">
         <v>5</v>
@@ -5321,7 +5402,7 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A195" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B195" s="4">
         <v>5</v>
@@ -5345,7 +5426,7 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A196" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B196" s="4">
         <v>7</v>
@@ -5369,7 +5450,7 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A197" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B197" s="4">
         <v>4</v>
@@ -5393,7 +5474,7 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A198" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B198" s="4">
         <v>10</v>
@@ -5417,7 +5498,7 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A199" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B199" s="4">
         <v>5</v>
@@ -5441,7 +5522,7 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A200" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B200" s="4">
         <v>3</v>
@@ -5465,7 +5546,7 @@
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A201" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B201" s="4">
         <v>8</v>
@@ -5489,7 +5570,7 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A202" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B202" s="4">
         <v>8</v>
@@ -5513,7 +5594,7 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A203" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B203" s="4">
         <v>7</v>
@@ -5537,7 +5618,7 @@
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A204" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B204" s="4">
         <v>7</v>
@@ -5561,7 +5642,7 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A205" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B205" s="4">
         <v>6</v>
@@ -5585,7 +5666,7 @@
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A206" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B206" s="4">
         <v>3</v>
@@ -5609,7 +5690,7 @@
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A207" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B207" s="4">
         <v>8</v>
@@ -5633,7 +5714,7 @@
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A208" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B208" s="4">
         <v>6</v>
@@ -5657,7 +5738,7 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A209" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B209" s="4">
         <v>6</v>
@@ -5681,7 +5762,7 @@
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A210" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B210" s="4">
         <v>7</v>
@@ -5705,7 +5786,7 @@
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A211" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B211" s="4">
         <v>5</v>
@@ -5729,7 +5810,7 @@
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A212" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B212" s="4">
         <v>7</v>
@@ -5753,7 +5834,7 @@
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A213" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B213" s="4">
         <v>6</v>
@@ -5777,7 +5858,7 @@
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A214" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B214" s="4">
         <v>8</v>
@@ -5801,7 +5882,7 @@
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A215" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B215" s="4">
         <v>4</v>
@@ -5825,7 +5906,7 @@
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A216" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B216" s="4">
         <v>9</v>
@@ -5849,7 +5930,7 @@
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A217" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B217" s="4">
         <v>11</v>
@@ -5873,7 +5954,7 @@
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A218" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B218" s="4">
         <v>6</v>
@@ -5897,7 +5978,7 @@
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A219" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B219" s="4">
         <v>3</v>
@@ -5921,7 +6002,7 @@
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A220" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B220" s="4">
         <v>4</v>
@@ -5945,7 +6026,7 @@
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A221" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B221" s="4">
         <v>3</v>
@@ -5969,7 +6050,7 @@
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A222" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B222" s="4">
         <v>11</v>
@@ -5993,7 +6074,7 @@
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A223" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B223" s="4">
         <v>5</v>
@@ -6017,7 +6098,7 @@
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A224" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B224" s="4">
         <v>8</v>
@@ -6041,7 +6122,7 @@
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A225" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B225" s="4">
         <v>5</v>
@@ -6065,7 +6146,7 @@
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A226" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B226" s="4">
         <v>9</v>
@@ -6089,7 +6170,7 @@
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A227" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B227" s="4">
         <v>10</v>
@@ -6113,7 +6194,7 @@
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A228" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B228" s="4">
         <v>4</v>
@@ -6137,7 +6218,7 @@
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A229" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B229" s="4">
         <v>7</v>
@@ -6161,7 +6242,7 @@
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A230" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B230" s="4">
         <v>8</v>
@@ -6185,7 +6266,7 @@
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A231" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B231" s="4">
         <v>4</v>
@@ -6209,7 +6290,7 @@
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A232" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B232" s="4">
         <v>4</v>
@@ -6233,7 +6314,7 @@
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A233" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B233" s="4">
         <v>3</v>
@@ -6257,7 +6338,7 @@
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A234" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B234" s="4">
         <v>3</v>
@@ -6281,7 +6362,7 @@
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A235" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B235" s="4">
         <v>6</v>
@@ -6305,7 +6386,7 @@
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A236" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B236" s="4">
         <v>7</v>
@@ -6329,7 +6410,7 @@
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A237" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B237" s="4">
         <v>8</v>
@@ -6353,7 +6434,7 @@
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A238" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B238" s="4">
         <v>4</v>
@@ -6377,7 +6458,7 @@
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A239" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B239" s="4">
         <v>10</v>
@@ -6401,7 +6482,7 @@
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A240" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B240" s="4">
         <v>4</v>
@@ -6425,7 +6506,7 @@
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A241" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B241" s="4">
         <v>10</v>
@@ -6449,7 +6530,7 @@
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A242" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B242" s="4">
         <v>6</v>
@@ -6473,7 +6554,7 @@
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A243" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B243" s="4">
         <v>12</v>
@@ -6497,7 +6578,7 @@
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A244" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B244" s="4">
         <v>8</v>
@@ -6521,7 +6602,7 @@
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A245" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B245" s="4">
         <v>6</v>
@@ -6545,7 +6626,7 @@
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A246" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B246" s="4">
         <v>3</v>
@@ -6569,7 +6650,7 @@
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A247" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B247" s="4">
         <v>3</v>
@@ -6593,7 +6674,7 @@
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A248" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B248" s="4">
         <v>10</v>
@@ -6617,7 +6698,7 @@
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A249" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B249" s="4">
         <v>5</v>
@@ -6641,7 +6722,7 @@
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A250" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B250" s="4">
         <v>4</v>
@@ -6665,7 +6746,7 @@
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A251" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B251" s="4">
         <v>5</v>
@@ -6689,7 +6770,7 @@
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A252" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B252" s="4">
         <v>4</v>
@@ -6713,7 +6794,7 @@
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A253" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B253" s="4">
         <v>5</v>
@@ -6737,7 +6818,7 @@
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A254" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B254" s="4">
         <v>4</v>
@@ -6761,7 +6842,7 @@
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A255" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B255" s="4">
         <v>4</v>
@@ -6785,7 +6866,7 @@
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A256" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B256" s="4">
         <v>7</v>
@@ -6809,7 +6890,7 @@
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A257" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B257" s="4">
         <v>5</v>
@@ -6833,7 +6914,7 @@
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A258" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B258" s="4">
         <v>4</v>
@@ -6857,7 +6938,7 @@
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A259" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B259" s="4">
         <v>7</v>
@@ -6881,7 +6962,7 @@
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A260" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B260" s="4">
         <v>8</v>
@@ -6905,7 +6986,7 @@
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A261" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B261" s="4">
         <v>6</v>
@@ -6929,7 +7010,7 @@
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A262" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B262" s="4">
         <v>7</v>
@@ -6953,7 +7034,7 @@
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A263" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B263" s="4">
         <v>6</v>
@@ -6977,7 +7058,7 @@
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A264" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B264" s="4">
         <v>9</v>
@@ -7001,7 +7082,7 @@
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A265" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B265" s="4">
         <v>7</v>
@@ -7025,7 +7106,7 @@
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A266" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B266" s="4">
         <v>5</v>
@@ -7049,7 +7130,7 @@
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A267" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B267" s="4">
         <v>8</v>
@@ -7073,7 +7154,7 @@
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A268" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B268" s="4">
         <v>8</v>
@@ -7097,7 +7178,7 @@
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A269" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B269" s="4">
         <v>9</v>
@@ -7121,7 +7202,7 @@
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A270" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B270" s="4">
         <v>9</v>
@@ -7145,7 +7226,7 @@
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A271" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B271" s="4">
         <v>8</v>
@@ -7169,7 +7250,7 @@
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A272" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B272" s="4">
         <v>5</v>
@@ -7193,7 +7274,7 @@
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A273" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B273" s="4">
         <v>11</v>
@@ -7217,7 +7298,7 @@
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A274" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B274" s="4">
         <v>6</v>
@@ -7241,7 +7322,7 @@
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A275" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B275" s="4">
         <v>5</v>
@@ -7265,7 +7346,7 @@
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A276" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B276" s="4">
         <v>7</v>
@@ -7289,7 +7370,7 @@
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A277" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B277" s="4">
         <v>7</v>
@@ -7313,7 +7394,7 @@
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A278" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B278" s="4">
         <v>4</v>
@@ -7337,7 +7418,7 @@
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A279" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B279" s="4">
         <v>10</v>
@@ -7361,7 +7442,7 @@
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A280" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B280" s="4">
         <v>6</v>
@@ -7385,7 +7466,7 @@
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A281" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B281" s="4">
         <v>6</v>
@@ -7409,7 +7490,7 @@
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A282" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B282" s="4">
         <v>7</v>
@@ -7433,7 +7514,7 @@
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A283" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B283" s="4">
         <v>8</v>
@@ -7457,7 +7538,7 @@
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A284" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B284" s="4">
         <v>3</v>
@@ -7481,7 +7562,7 @@
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A285" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B285" s="4">
         <v>4</v>
@@ -7505,7 +7586,7 @@
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A286" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B286" s="4">
         <v>4</v>
@@ -7529,7 +7610,7 @@
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A287" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B287" s="4">
         <v>5</v>
@@ -7553,7 +7634,7 @@
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A288" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B288" s="4">
         <v>6</v>
@@ -7577,7 +7658,7 @@
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A289" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B289" s="4">
         <v>8</v>
@@ -7601,7 +7682,7 @@
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A290" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B290" s="4">
         <v>4</v>
@@ -7625,7 +7706,7 @@
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A291" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B291" s="4">
         <v>10</v>
@@ -7649,7 +7730,7 @@
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A292" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B292" s="4">
         <v>7</v>
@@ -7673,7 +7754,7 @@
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A293" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B293" s="4">
         <v>6</v>
@@ -7697,7 +7778,7 @@
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A294" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B294" s="4">
         <v>9</v>
@@ -7721,7 +7802,7 @@
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A295" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B295" s="4">
         <v>5</v>
@@ -7745,7 +7826,7 @@
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A296" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B296" s="4">
         <v>11</v>
@@ -7769,7 +7850,7 @@
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A297" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B297" s="4">
         <v>4</v>
@@ -7793,7 +7874,7 @@
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A298" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B298" s="4">
         <v>7</v>
@@ -7817,7 +7898,7 @@
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A299" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B299" s="4">
         <v>10</v>
@@ -7841,7 +7922,7 @@
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A300" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B300" s="4">
         <v>7</v>
@@ -7865,7 +7946,7 @@
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A301" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B301" s="4">
         <v>7</v>
@@ -7889,7 +7970,7 @@
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A302" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B302" s="4">
         <v>6</v>
@@ -7913,7 +7994,7 @@
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A303" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B303" s="4">
         <v>8</v>
@@ -7937,7 +8018,7 @@
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A304" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B304" s="4">
         <v>4</v>
@@ -7961,7 +8042,7 @@
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A305" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B305" s="4">
         <v>5</v>
@@ -7985,7 +8066,7 @@
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A306" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B306" s="4">
         <v>7</v>
@@ -8009,7 +8090,7 @@
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A307" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B307" s="4">
         <v>5</v>
@@ -8033,7 +8114,7 @@
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A308" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B308" s="4">
         <v>6</v>
@@ -8057,7 +8138,7 @@
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A309" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B309" s="4">
         <v>9</v>
@@ -8081,7 +8162,7 @@
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A310" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B310" s="4">
         <v>9</v>
@@ -8105,7 +8186,7 @@
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A311" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B311" s="4">
         <v>5</v>
@@ -8129,7 +8210,7 @@
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A312" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B312" s="4">
         <v>8</v>
@@ -8153,7 +8234,7 @@
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A313" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B313" s="4">
         <v>3</v>
@@ -8177,7 +8258,7 @@
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A314" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B314" s="4">
         <v>9</v>
@@ -8201,7 +8282,7 @@
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A315" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B315" s="4">
         <v>3</v>
@@ -8225,7 +8306,7 @@
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A316" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B316" s="4">
         <v>3</v>
@@ -8249,7 +8330,7 @@
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A317" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B317" s="4">
         <v>6</v>
@@ -8273,7 +8354,7 @@
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A318" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B318" s="4">
         <v>6</v>
@@ -8297,7 +8378,7 @@
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A319" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B319" s="4">
         <v>11</v>
@@ -8321,7 +8402,7 @@
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A320" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B320" s="4">
         <v>4</v>
@@ -8345,7 +8426,7 @@
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A321" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B321" s="4">
         <v>6</v>
@@ -8369,7 +8450,7 @@
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A322" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B322" s="4">
         <v>10</v>
@@ -8393,7 +8474,7 @@
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A323" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B323" s="4">
         <v>6</v>
@@ -8417,7 +8498,7 @@
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A324" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B324" s="4">
         <v>6</v>
@@ -8441,7 +8522,7 @@
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A325" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B325" s="4">
         <v>9</v>
@@ -8465,7 +8546,7 @@
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A326" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B326" s="4">
         <v>6</v>
@@ -8489,7 +8570,7 @@
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A327" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B327" s="4">
         <v>3</v>
@@ -8513,7 +8594,7 @@
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A328" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B328" s="4">
         <v>5</v>
@@ -8537,7 +8618,7 @@
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A329" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B329" s="4">
         <v>4</v>
@@ -8561,7 +8642,7 @@
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A330" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B330" s="4">
         <v>7</v>
@@ -8585,7 +8666,7 @@
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A331" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B331" s="4">
         <v>7</v>
@@ -8609,7 +8690,7 @@
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A332" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B332" s="4">
         <v>5</v>
@@ -8636,23 +8717,23 @@
         <v>30</v>
       </c>
       <c r="B333" s="4">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C333" s="14">
         <f>_xlfn.XLOOKUP(B333,'Average Salary'!A:A,'Average Salary'!B:B)</f>
-        <v>361055.48698113207</v>
+        <v>25070.000000000004</v>
       </c>
       <c r="D333" s="14">
         <f>_xlfn.XLOOKUP($B333,'Average Salary'!$A:$A,'Average Salary'!C:C)</f>
-        <v>3530</v>
+        <v>0</v>
       </c>
       <c r="E333" s="14">
         <f>_xlfn.XLOOKUP($B333,'Average Salary'!$A:$A,'Average Salary'!D:D)</f>
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F333" s="14">
         <f>_xlfn.XLOOKUP($B333,'Average Salary'!$A:$A,'Average Salary'!E:E)</f>
-        <v>2500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.35">
@@ -8660,23 +8741,23 @@
         <v>30</v>
       </c>
       <c r="B334" s="4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C334" s="14">
         <f>_xlfn.XLOOKUP(B334,'Average Salary'!A:A,'Average Salary'!B:B)</f>
-        <v>62130.000000000007</v>
+        <v>25070.000000000004</v>
       </c>
       <c r="D334" s="14">
         <f>_xlfn.XLOOKUP($B334,'Average Salary'!$A:$A,'Average Salary'!C:C)</f>
-        <v>3530</v>
+        <v>0</v>
       </c>
       <c r="E334" s="14">
         <f>_xlfn.XLOOKUP($B334,'Average Salary'!$A:$A,'Average Salary'!D:D)</f>
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F334" s="14">
         <f>_xlfn.XLOOKUP($B334,'Average Salary'!$A:$A,'Average Salary'!E:E)</f>
-        <v>1553.2500000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.35">
@@ -8684,23 +8765,23 @@
         <v>30</v>
       </c>
       <c r="B335" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C335" s="14">
         <f>_xlfn.XLOOKUP(B335,'Average Salary'!A:A,'Average Salary'!B:B)</f>
-        <v>42510</v>
+        <v>25070.000000000004</v>
       </c>
       <c r="D335" s="14">
         <f>_xlfn.XLOOKUP($B335,'Average Salary'!$A:$A,'Average Salary'!C:C)</f>
-        <v>3530</v>
+        <v>0</v>
       </c>
       <c r="E335" s="14">
         <f>_xlfn.XLOOKUP($B335,'Average Salary'!$A:$A,'Average Salary'!D:D)</f>
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F335" s="14">
         <f>_xlfn.XLOOKUP($B335,'Average Salary'!$A:$A,'Average Salary'!E:E)</f>
-        <v>1062.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.35">
@@ -8708,23 +8789,23 @@
         <v>30</v>
       </c>
       <c r="B336" s="4">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C336" s="14">
         <f>_xlfn.XLOOKUP(B336,'Average Salary'!A:A,'Average Salary'!B:B)</f>
-        <v>115927.90920000001</v>
+        <v>25070.000000000004</v>
       </c>
       <c r="D336" s="14">
         <f>_xlfn.XLOOKUP($B336,'Average Salary'!$A:$A,'Average Salary'!C:C)</f>
-        <v>3530</v>
+        <v>0</v>
       </c>
       <c r="E336" s="14">
         <f>_xlfn.XLOOKUP($B336,'Average Salary'!$A:$A,'Average Salary'!D:D)</f>
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F336" s="14">
         <f>_xlfn.XLOOKUP($B336,'Average Salary'!$A:$A,'Average Salary'!E:E)</f>
-        <v>2500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.35">
@@ -8732,28 +8813,28 @@
         <v>30</v>
       </c>
       <c r="B337" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C337" s="14">
         <f>_xlfn.XLOOKUP(B337,'Average Salary'!A:A,'Average Salary'!B:B)</f>
-        <v>42510</v>
+        <v>25070.000000000004</v>
       </c>
       <c r="D337" s="14">
         <f>_xlfn.XLOOKUP($B337,'Average Salary'!$A:$A,'Average Salary'!C:C)</f>
-        <v>3530</v>
+        <v>0</v>
       </c>
       <c r="E337" s="14">
         <f>_xlfn.XLOOKUP($B337,'Average Salary'!$A:$A,'Average Salary'!D:D)</f>
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F337" s="14">
         <f>_xlfn.XLOOKUP($B337,'Average Salary'!$A:$A,'Average Salary'!E:E)</f>
-        <v>1062.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A338" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B338" s="4">
         <v>2</v>
@@ -8777,7 +8858,7 @@
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A339" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B339" s="4">
         <v>2</v>
@@ -8801,7 +8882,7 @@
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A340" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B340" s="4">
         <v>2</v>
@@ -8825,7 +8906,7 @@
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A341" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B341" s="4">
         <v>2</v>
@@ -8849,7 +8930,7 @@
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A342" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B342" s="4">
         <v>2</v>
@@ -8873,7 +8954,7 @@
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A343" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B343" s="4">
         <v>2</v>
@@ -8897,7 +8978,7 @@
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A344" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B344" s="4">
         <v>2</v>
@@ -8921,7 +9002,7 @@
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A345" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B345" s="4">
         <v>2</v>
@@ -8945,7 +9026,7 @@
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A346" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B346" s="4">
         <v>2</v>
@@ -8969,7 +9050,7 @@
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A347" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B347" s="4">
         <v>2</v>
@@ -8993,7 +9074,7 @@
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A348" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B348" s="4">
         <v>2</v>
@@ -9017,7 +9098,7 @@
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A349" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B349" s="4">
         <v>2</v>
@@ -9041,7 +9122,7 @@
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A350" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B350" s="4">
         <v>2</v>
@@ -9065,7 +9146,7 @@
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A351" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B351" s="4">
         <v>2</v>
@@ -9087,135 +9168,200 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A352" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B352" s="4">
-        <v>2</v>
-      </c>
-      <c r="C352" s="14">
-        <f>_xlfn.XLOOKUP(B352,'Average Salary'!A:A,'Average Salary'!B:B)</f>
-        <v>25070.000000000004</v>
-      </c>
-      <c r="D352" s="14">
-        <f>_xlfn.XLOOKUP($B352,'Average Salary'!$A:$A,'Average Salary'!C:C)</f>
-        <v>0</v>
-      </c>
-      <c r="E352" s="14">
-        <f>_xlfn.XLOOKUP($B352,'Average Salary'!$A:$A,'Average Salary'!D:D)</f>
-        <v>0</v>
-      </c>
-      <c r="F352" s="14">
-        <f>_xlfn.XLOOKUP($B352,'Average Salary'!$A:$A,'Average Salary'!E:E)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="353" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A353" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B353" s="4">
-        <v>2</v>
-      </c>
-      <c r="C353" s="14">
-        <f>_xlfn.XLOOKUP(B353,'Average Salary'!A:A,'Average Salary'!B:B)</f>
-        <v>25070.000000000004</v>
-      </c>
-      <c r="D353" s="14">
-        <f>_xlfn.XLOOKUP($B353,'Average Salary'!$A:$A,'Average Salary'!C:C)</f>
-        <v>0</v>
-      </c>
-      <c r="E353" s="14">
-        <f>_xlfn.XLOOKUP($B353,'Average Salary'!$A:$A,'Average Salary'!D:D)</f>
-        <v>0</v>
-      </c>
-      <c r="F353" s="14">
-        <f>_xlfn.XLOOKUP($B353,'Average Salary'!$A:$A,'Average Salary'!E:E)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A354" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B354" s="4">
-        <v>2</v>
-      </c>
-      <c r="C354" s="14">
-        <f>_xlfn.XLOOKUP(B354,'Average Salary'!A:A,'Average Salary'!B:B)</f>
-        <v>25070.000000000004</v>
-      </c>
-      <c r="D354" s="14">
-        <f>_xlfn.XLOOKUP($B354,'Average Salary'!$A:$A,'Average Salary'!C:C)</f>
-        <v>0</v>
-      </c>
-      <c r="E354" s="14">
-        <f>_xlfn.XLOOKUP($B354,'Average Salary'!$A:$A,'Average Salary'!D:D)</f>
-        <v>0</v>
-      </c>
-      <c r="F354" s="14">
-        <f>_xlfn.XLOOKUP($B354,'Average Salary'!$A:$A,'Average Salary'!E:E)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A355" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B355" s="4">
-        <v>2</v>
-      </c>
-      <c r="C355" s="14">
-        <f>_xlfn.XLOOKUP(B355,'Average Salary'!A:A,'Average Salary'!B:B)</f>
-        <v>25070.000000000004</v>
-      </c>
-      <c r="D355" s="14">
-        <f>_xlfn.XLOOKUP($B355,'Average Salary'!$A:$A,'Average Salary'!C:C)</f>
-        <v>0</v>
-      </c>
-      <c r="E355" s="14">
-        <f>_xlfn.XLOOKUP($B355,'Average Salary'!$A:$A,'Average Salary'!D:D)</f>
-        <v>0</v>
-      </c>
-      <c r="F355" s="14">
-        <f>_xlfn.XLOOKUP($B355,'Average Salary'!$A:$A,'Average Salary'!E:E)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A356" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B356" s="4">
-        <v>2</v>
-      </c>
-      <c r="C356" s="14">
-        <f>_xlfn.XLOOKUP(B356,'Average Salary'!A:A,'Average Salary'!B:B)</f>
-        <v>25070.000000000004</v>
-      </c>
-      <c r="D356" s="14">
-        <f>_xlfn.XLOOKUP($B356,'Average Salary'!$A:$A,'Average Salary'!C:C)</f>
-        <v>0</v>
-      </c>
-      <c r="E356" s="14">
-        <f>_xlfn.XLOOKUP($B356,'Average Salary'!$A:$A,'Average Salary'!D:D)</f>
-        <v>0</v>
-      </c>
-      <c r="F356" s="14">
-        <f>_xlfn.XLOOKUP($B356,'Average Salary'!$A:$A,'Average Salary'!E:E)</f>
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A7:F356" xr:uid="{789E7D11-EEEA-4C1D-B28D-993BA3CC8ADE}"/>
+  <autoFilter ref="A7:F351" xr:uid="{789E7D11-EEEA-4C1D-B28D-993BA3CC8ADE}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D49C2A82-4498-40F3-8ACA-1E3C7D5B7111}">
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="36.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="19.08984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="25"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="25"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="1">
+        <f>('Headcount per Company'!B6*'Average Salary'!$B6)+('Headcount per Company'!B7*'Average Salary'!$B7)+('Headcount per Company'!B8*'Average Salary'!$B8)+('Headcount per Company'!B9*'Average Salary'!$B9)+('Headcount per Company'!B10*'Average Salary'!$B10)+('Headcount per Company'!B11*'Average Salary'!$B11)+('Headcount per Company'!B12*'Average Salary'!$B12)+('Headcount per Company'!B13*'Average Salary'!$B13)+('Headcount per Company'!B14*'Average Salary'!$B14)+('Headcount per Company'!B15*'Average Salary'!$B15)+('Headcount per Company'!B16*'Average Salary'!$B16)+('Headcount per Company'!B17*'Average Salary'!$B17)</f>
+        <v>19250463.755373586</v>
+      </c>
+      <c r="C7" s="1">
+        <f>('Headcount per Company'!C6*'Average Salary'!$B6)+('Headcount per Company'!C7*'Average Salary'!$B7)+('Headcount per Company'!C8*'Average Salary'!$B8)+('Headcount per Company'!C9*'Average Salary'!$B9)+('Headcount per Company'!C10*'Average Salary'!$B10)+('Headcount per Company'!C11*'Average Salary'!$B11)+('Headcount per Company'!C12*'Average Salary'!$B12)+('Headcount per Company'!C13*'Average Salary'!$B13)+('Headcount per Company'!C14*'Average Salary'!$B14)+('Headcount per Company'!C15*'Average Salary'!$B15)+('Headcount per Company'!C16*'Average Salary'!$B16)+('Headcount per Company'!C17*'Average Salary'!$B17)</f>
+        <v>4660714.9551999997</v>
+      </c>
+      <c r="D7" s="1">
+        <f>('Headcount per Company'!D6*'Average Salary'!$B6)+('Headcount per Company'!D7*'Average Salary'!$B7)+('Headcount per Company'!D8*'Average Salary'!$B8)+('Headcount per Company'!D9*'Average Salary'!$B9)+('Headcount per Company'!D10*'Average Salary'!$B10)+('Headcount per Company'!D11*'Average Salary'!$B11)+('Headcount per Company'!D12*'Average Salary'!$B12)+('Headcount per Company'!D13*'Average Salary'!$B13)+('Headcount per Company'!D14*'Average Salary'!$B14)+('Headcount per Company'!D15*'Average Salary'!$B15)+('Headcount per Company'!D16*'Average Salary'!$B16)+('Headcount per Company'!D17*'Average Salary'!$B17)</f>
+        <v>2743998.0024000001</v>
+      </c>
+      <c r="E7" s="1">
+        <f>SUM(B7:D7)</f>
+        <v>26655176.712973583</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="1">
+        <f>B7*2/12</f>
+        <v>3208410.6258955975</v>
+      </c>
+      <c r="C8" s="1">
+        <f>C7*2/12</f>
+        <v>776785.82586666662</v>
+      </c>
+      <c r="D8" s="1">
+        <f>D7*2/12</f>
+        <v>457333.00040000002</v>
+      </c>
+      <c r="E8" s="1">
+        <f t="shared" ref="E8:E9" si="0">SUM(B8:D8)</f>
+        <v>4442529.4521622639</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" s="1">
+        <f>('Headcount per Company'!B6*'Average Salary'!$C6)+('Headcount per Company'!B7*'Average Salary'!$C7)+('Headcount per Company'!B8*'Average Salary'!$C8)+('Headcount per Company'!B9*'Average Salary'!$C9)+('Headcount per Company'!B10*'Average Salary'!$C10)+('Headcount per Company'!B11*'Average Salary'!$C11)+('Headcount per Company'!B12*'Average Salary'!$C12)+('Headcount per Company'!B13*'Average Salary'!$C13)+('Headcount per Company'!B14*'Average Salary'!$C14)+('Headcount per Company'!B15*'Average Salary'!$C15)+('Headcount per Company'!B16*'Average Salary'!$C16)+('Headcount per Company'!B17*'Average Salary'!$C17)</f>
+        <v>603110</v>
+      </c>
+      <c r="C9" s="1">
+        <f>('Headcount per Company'!C6*'Average Salary'!$C6)+('Headcount per Company'!C7*'Average Salary'!$C7)+('Headcount per Company'!C8*'Average Salary'!$C8)+('Headcount per Company'!C9*'Average Salary'!$C9)+('Headcount per Company'!C10*'Average Salary'!$C10)+('Headcount per Company'!C11*'Average Salary'!$C11)+('Headcount per Company'!C12*'Average Salary'!$C12)+('Headcount per Company'!C13*'Average Salary'!$C13)+('Headcount per Company'!C14*'Average Salary'!$C14)+('Headcount per Company'!C15*'Average Salary'!$C15)+('Headcount per Company'!C16*'Average Salary'!$C16)+('Headcount per Company'!C17*'Average Salary'!$C17)</f>
+        <v>278250</v>
+      </c>
+      <c r="D9" s="1">
+        <f>('Headcount per Company'!D6*'Average Salary'!$C6)+('Headcount per Company'!D7*'Average Salary'!$C7)+('Headcount per Company'!D8*'Average Salary'!$C8)+('Headcount per Company'!D9*'Average Salary'!$C9)+('Headcount per Company'!D10*'Average Salary'!$C10)+('Headcount per Company'!D11*'Average Salary'!$C11)+('Headcount per Company'!D12*'Average Salary'!$C12)+('Headcount per Company'!D13*'Average Salary'!$C13)+('Headcount per Company'!D14*'Average Salary'!$C14)+('Headcount per Company'!D15*'Average Salary'!$C15)+('Headcount per Company'!D16*'Average Salary'!$C16)+('Headcount per Company'!D17*'Average Salary'!$C17)</f>
+        <v>202490</v>
+      </c>
+      <c r="E9" s="1">
+        <f t="shared" si="0"/>
+        <v>1083850</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="1">
+        <f>('Headcount per Company'!B6*'Average Salary'!$D6)+('Headcount per Company'!B7*'Average Salary'!$D7)+('Headcount per Company'!B8*'Average Salary'!$D8)+('Headcount per Company'!B9*'Average Salary'!$D9)+('Headcount per Company'!B10*'Average Salary'!$D10)+('Headcount per Company'!B11*'Average Salary'!$D11)+('Headcount per Company'!B12*'Average Salary'!$D12)+('Headcount per Company'!B13*'Average Salary'!$D13)+('Headcount per Company'!B14*'Average Salary'!$D14)+('Headcount per Company'!B15*'Average Salary'!$D15)+('Headcount per Company'!B16*'Average Salary'!$D16)+('Headcount per Company'!B17*'Average Salary'!$D17)</f>
+        <v>35400</v>
+      </c>
+      <c r="C10" s="1">
+        <f>('Headcount per Company'!C6*'Average Salary'!$D6)+('Headcount per Company'!C7*'Average Salary'!$D7)+('Headcount per Company'!C8*'Average Salary'!$D8)+('Headcount per Company'!C9*'Average Salary'!$D9)+('Headcount per Company'!C10*'Average Salary'!$D10)+('Headcount per Company'!C11*'Average Salary'!$D11)+('Headcount per Company'!C12*'Average Salary'!$D12)+('Headcount per Company'!C13*'Average Salary'!$D13)+('Headcount per Company'!C14*'Average Salary'!$D14)+('Headcount per Company'!C15*'Average Salary'!$D15)+('Headcount per Company'!C16*'Average Salary'!$D16)+('Headcount per Company'!C17*'Average Salary'!$D17)</f>
+        <v>17000</v>
+      </c>
+      <c r="D10" s="1">
+        <f>('Headcount per Company'!D6*'Average Salary'!$D6)+('Headcount per Company'!D7*'Average Salary'!$D7)+('Headcount per Company'!D8*'Average Salary'!$D8)+('Headcount per Company'!D9*'Average Salary'!$D9)+('Headcount per Company'!D10*'Average Salary'!$D10)+('Headcount per Company'!D11*'Average Salary'!$D11)+('Headcount per Company'!D12*'Average Salary'!$D12)+('Headcount per Company'!D13*'Average Salary'!$D13)+('Headcount per Company'!D14*'Average Salary'!$D14)+('Headcount per Company'!D15*'Average Salary'!$D15)+('Headcount per Company'!D16*'Average Salary'!$D16)+('Headcount per Company'!D17*'Average Salary'!$D17)</f>
+        <v>12600</v>
+      </c>
+      <c r="E10" s="1">
+        <f>SUM(B10:D10)</f>
+        <v>65000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" s="24">
+        <f>('Headcount per Company'!B6*'Average Salary'!$E6)+('Headcount per Company'!B7*'Average Salary'!$E7)+('Headcount per Company'!B8*'Average Salary'!$E8)+('Headcount per Company'!B9*'Average Salary'!$E9)+('Headcount per Company'!B10*'Average Salary'!$E10)+('Headcount per Company'!B11*'Average Salary'!$E11)+('Headcount per Company'!B12*'Average Salary'!$E12)+('Headcount per Company'!B13*'Average Salary'!$E13)+('Headcount per Company'!B14*'Average Salary'!$E14)+('Headcount per Company'!B15*'Average Salary'!$E15)+('Headcount per Company'!B16*'Average Salary'!$E16)+('Headcount per Company'!B17*'Average Salary'!$E17)</f>
+        <v>282465.94092000002</v>
+      </c>
+      <c r="C11" s="24">
+        <f>('Headcount per Company'!C6*'Average Salary'!$E6)+('Headcount per Company'!C7*'Average Salary'!$E7)+('Headcount per Company'!C8*'Average Salary'!$E8)+('Headcount per Company'!C9*'Average Salary'!$E9)+('Headcount per Company'!C10*'Average Salary'!$E10)+('Headcount per Company'!C11*'Average Salary'!$E11)+('Headcount per Company'!C12*'Average Salary'!$E12)+('Headcount per Company'!C13*'Average Salary'!$E13)+('Headcount per Company'!C14*'Average Salary'!$E14)+('Headcount per Company'!C15*'Average Salary'!$E15)+('Headcount per Company'!C16*'Average Salary'!$E16)+('Headcount per Company'!C17*'Average Salary'!$E17)</f>
+        <v>99686</v>
+      </c>
+      <c r="D11" s="24">
+        <f>('Headcount per Company'!D6*'Average Salary'!$E6)+('Headcount per Company'!D7*'Average Salary'!$E7)+('Headcount per Company'!D8*'Average Salary'!$E8)+('Headcount per Company'!D9*'Average Salary'!$E9)+('Headcount per Company'!D10*'Average Salary'!$E10)+('Headcount per Company'!D11*'Average Salary'!$E11)+('Headcount per Company'!D12*'Average Salary'!$E12)+('Headcount per Company'!D13*'Average Salary'!$E13)+('Headcount per Company'!D14*'Average Salary'!$E14)+('Headcount per Company'!D15*'Average Salary'!$E15)+('Headcount per Company'!D16*'Average Salary'!$E16)+('Headcount per Company'!D17*'Average Salary'!$E17)</f>
+        <v>66210.763680000004</v>
+      </c>
+      <c r="E11" s="24">
+        <f>SUM(B11:D11)</f>
+        <v>448362.70460000006</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="1">
+        <f>SUM(B7:B11)</f>
+        <v>23379850.322189182</v>
+      </c>
+      <c r="C12" s="1">
+        <f t="shared" ref="C12:E12" si="1">SUM(C7:C11)</f>
+        <v>5832436.7810666664</v>
+      </c>
+      <c r="D12" s="1">
+        <f t="shared" si="1"/>
+        <v>3482631.7664799998</v>
+      </c>
+      <c r="E12" s="1">
+        <f t="shared" si="1"/>
+        <v>32694918.869735844</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E13" s="1">
+        <f>E12-E8</f>
+        <v>28252389.417573579</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E14" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B21C9AB4-7127-4C64-AD57-62D31C4B256F}">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.36328125" style="2" customWidth="1"/>
@@ -9228,12 +9374,12 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -9241,24 +9387,24 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B4" s="5" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="17" t="s">
         <v>5</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>6</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>0</v>
@@ -9488,6 +9634,12 @@
       <c r="E17" s="13">
         <v>2500</v>
       </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B18" s="1"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B19" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9495,7 +9647,342 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F9C0CF6-0EDA-4444-853D-1F1783FC5582}">
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="13.26953125" customWidth="1"/>
+    <col min="2" max="4" width="19.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="2">
+        <v>1</v>
+      </c>
+      <c r="B6" s="4">
+        <f>COUNTIFS('Employee List'!$B:$B,'Headcount per Company'!$A6,'Employee List'!$A:$A,'Headcount per Company'!B$5)</f>
+        <v>4</v>
+      </c>
+      <c r="C6" s="4">
+        <f>COUNTIFS('Employee List'!$B:$B,'Headcount per Company'!$A6,'Employee List'!$A:$A,'Headcount per Company'!C$5)</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="4">
+        <f>COUNTIFS('Employee List'!$B:$B,'Headcount per Company'!$A6,'Employee List'!$A:$A,'Headcount per Company'!D$5)</f>
+        <v>16</v>
+      </c>
+      <c r="E6">
+        <f t="shared" ref="E6:E17" si="0">SUM(B6:D6)</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="2">
+        <v>2</v>
+      </c>
+      <c r="B7" s="4">
+        <f>COUNTIFS('Employee List'!$B:$B,'Headcount per Company'!$A7,'Employee List'!$A:$A,'Headcount per Company'!B$5)</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="4">
+        <f>COUNTIFS('Employee List'!$B:$B,'Headcount per Company'!$A7,'Employee List'!$A:$A,'Headcount per Company'!C$5)</f>
+        <v>19</v>
+      </c>
+      <c r="D7" s="4">
+        <f>COUNTIFS('Employee List'!$B:$B,'Headcount per Company'!$A7,'Employee List'!$A:$A,'Headcount per Company'!D$5)</f>
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="2">
+        <v>3</v>
+      </c>
+      <c r="B8" s="4">
+        <f>COUNTIFS('Employee List'!$B:$B,'Headcount per Company'!$A8,'Employee List'!$A:$A,'Headcount per Company'!B$5)</f>
+        <v>18</v>
+      </c>
+      <c r="C8" s="4">
+        <f>COUNTIFS('Employee List'!$B:$B,'Headcount per Company'!$A8,'Employee List'!$A:$A,'Headcount per Company'!C$5)</f>
+        <v>20</v>
+      </c>
+      <c r="D8" s="4">
+        <f>COUNTIFS('Employee List'!$B:$B,'Headcount per Company'!$A8,'Employee List'!$A:$A,'Headcount per Company'!D$5)</f>
+        <v>15</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" s="2">
+        <f>A8+1</f>
+        <v>4</v>
+      </c>
+      <c r="B9" s="4">
+        <f>COUNTIFS('Employee List'!$B:$B,'Headcount per Company'!$A9,'Employee List'!$A:$A,'Headcount per Company'!B$5)</f>
+        <v>27</v>
+      </c>
+      <c r="C9" s="4">
+        <f>COUNTIFS('Employee List'!$B:$B,'Headcount per Company'!$A9,'Employee List'!$A:$A,'Headcount per Company'!C$5)</f>
+        <v>18</v>
+      </c>
+      <c r="D9" s="4">
+        <f>COUNTIFS('Employee List'!$B:$B,'Headcount per Company'!$A9,'Employee List'!$A:$A,'Headcount per Company'!D$5)</f>
+        <v>9</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" s="2">
+        <f t="shared" ref="A10:A17" si="1">A9+1</f>
+        <v>5</v>
+      </c>
+      <c r="B10" s="4">
+        <f>COUNTIFS('Employee List'!$B:$B,'Headcount per Company'!$A10,'Employee List'!$A:$A,'Headcount per Company'!B$5)</f>
+        <v>24</v>
+      </c>
+      <c r="C10" s="4">
+        <f>COUNTIFS('Employee List'!$B:$B,'Headcount per Company'!$A10,'Employee List'!$A:$A,'Headcount per Company'!C$5)</f>
+        <v>24</v>
+      </c>
+      <c r="D10" s="4">
+        <f>COUNTIFS('Employee List'!$B:$B,'Headcount per Company'!$A10,'Employee List'!$A:$A,'Headcount per Company'!D$5)</f>
+        <v>13</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" s="2">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="B11" s="4">
+        <f>COUNTIFS('Employee List'!$B:$B,'Headcount per Company'!$A11,'Employee List'!$A:$A,'Headcount per Company'!B$5)</f>
+        <v>29</v>
+      </c>
+      <c r="C11" s="4">
+        <f>COUNTIFS('Employee List'!$B:$B,'Headcount per Company'!$A11,'Employee List'!$A:$A,'Headcount per Company'!C$5)</f>
+        <v>6</v>
+      </c>
+      <c r="D11" s="4">
+        <f>COUNTIFS('Employee List'!$B:$B,'Headcount per Company'!$A11,'Employee List'!$A:$A,'Headcount per Company'!D$5)</f>
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" s="2">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="B12" s="4">
+        <f>COUNTIFS('Employee List'!$B:$B,'Headcount per Company'!$A12,'Employee List'!$A:$A,'Headcount per Company'!B$5)</f>
+        <v>24</v>
+      </c>
+      <c r="C12" s="4">
+        <f>COUNTIFS('Employee List'!$B:$B,'Headcount per Company'!$A12,'Employee List'!$A:$A,'Headcount per Company'!C$5)</f>
+        <v>10</v>
+      </c>
+      <c r="D12" s="4">
+        <f>COUNTIFS('Employee List'!$B:$B,'Headcount per Company'!$A12,'Employee List'!$A:$A,'Headcount per Company'!D$5)</f>
+        <v>3</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" s="2">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="B13" s="4">
+        <f>COUNTIFS('Employee List'!$B:$B,'Headcount per Company'!$A13,'Employee List'!$A:$A,'Headcount per Company'!B$5)</f>
+        <v>19</v>
+      </c>
+      <c r="C13" s="4">
+        <f>COUNTIFS('Employee List'!$B:$B,'Headcount per Company'!$A13,'Employee List'!$A:$A,'Headcount per Company'!C$5)</f>
+        <v>6</v>
+      </c>
+      <c r="D13" s="4">
+        <f>COUNTIFS('Employee List'!$B:$B,'Headcount per Company'!$A13,'Employee List'!$A:$A,'Headcount per Company'!D$5)</f>
+        <v>6</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" s="2">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="B14" s="4">
+        <f>COUNTIFS('Employee List'!$B:$B,'Headcount per Company'!$A14,'Employee List'!$A:$A,'Headcount per Company'!B$5)</f>
+        <v>12</v>
+      </c>
+      <c r="C14" s="4">
+        <f>COUNTIFS('Employee List'!$B:$B,'Headcount per Company'!$A14,'Employee List'!$A:$A,'Headcount per Company'!C$5)</f>
+        <v>1</v>
+      </c>
+      <c r="D14" s="4">
+        <f>COUNTIFS('Employee List'!$B:$B,'Headcount per Company'!$A14,'Employee List'!$A:$A,'Headcount per Company'!D$5)</f>
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" s="2">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="B15" s="4">
+        <f>COUNTIFS('Employee List'!$B:$B,'Headcount per Company'!$A15,'Employee List'!$A:$A,'Headcount per Company'!B$5)</f>
+        <v>12</v>
+      </c>
+      <c r="C15" s="4">
+        <f>COUNTIFS('Employee List'!$B:$B,'Headcount per Company'!$A15,'Employee List'!$A:$A,'Headcount per Company'!C$5)</f>
+        <v>0</v>
+      </c>
+      <c r="D15" s="4">
+        <f>COUNTIFS('Employee List'!$B:$B,'Headcount per Company'!$A15,'Employee List'!$A:$A,'Headcount per Company'!D$5)</f>
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" s="2">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="B16" s="4">
+        <f>COUNTIFS('Employee List'!$B:$B,'Headcount per Company'!$A16,'Employee List'!$A:$A,'Headcount per Company'!B$5)</f>
+        <v>7</v>
+      </c>
+      <c r="C16" s="4">
+        <f>COUNTIFS('Employee List'!$B:$B,'Headcount per Company'!$A16,'Employee List'!$A:$A,'Headcount per Company'!C$5)</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="4">
+        <f>COUNTIFS('Employee List'!$B:$B,'Headcount per Company'!$A16,'Employee List'!$A:$A,'Headcount per Company'!D$5)</f>
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" s="2">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B17" s="20">
+        <f>COUNTIFS('Employee List'!$B:$B,'Headcount per Company'!$A17,'Employee List'!$A:$A,'Headcount per Company'!B$5)</f>
+        <v>1</v>
+      </c>
+      <c r="C17" s="20">
+        <f>COUNTIFS('Employee List'!$B:$B,'Headcount per Company'!$A17,'Employee List'!$A:$A,'Headcount per Company'!C$5)</f>
+        <v>0</v>
+      </c>
+      <c r="D17" s="20">
+        <f>COUNTIFS('Employee List'!$B:$B,'Headcount per Company'!$A17,'Employee List'!$A:$A,'Headcount per Company'!D$5)</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="21">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18">
+        <f>SUM(B6:B17)</f>
+        <v>177</v>
+      </c>
+      <c r="C18">
+        <f t="shared" ref="C18:E18" si="2">SUM(C6:C17)</f>
+        <v>104</v>
+      </c>
+      <c r="D18">
+        <f t="shared" si="2"/>
+        <v>63</v>
+      </c>
+      <c r="E18">
+        <f t="shared" si="2"/>
+        <v>344</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0772C1BA-BBCD-418E-A0A5-FF4D5711A87A}">
   <dimension ref="A1:I72"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -9511,56 +9998,56 @@
   <sheetData>
     <row r="1" spans="1:9" ht="21" x14ac:dyDescent="0.5">
       <c r="A1" s="6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="7"/>
     </row>
     <row r="4" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="27"/>
+      <c r="C4" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="20"/>
-      <c r="C4" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="24"/>
-      <c r="H4" s="24"/>
-      <c r="I4" s="24"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
     </row>
     <row r="5" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="D5" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="E5" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="F5" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="I5" s="8" t="s">
         <v>19</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
@@ -11608,7 +12095,7 @@
         <v>34750</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C66" s="9">
         <v>20000</v>
@@ -11639,27 +12126,27 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A68" s="12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A69" s="7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A70" s="7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A71" s="7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A72" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
